--- a/artfynd/A 30076-2025 artfynd.xlsx
+++ b/artfynd/A 30076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>56826915</v>
+        <v>56826903</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>646995.008611265</v>
+        <v>646915</v>
       </c>
       <c r="R2" t="n">
-        <v>7132879.068312062</v>
+        <v>7132902</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>björk</t>
+          <t>mossig gammal tallåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>56826908</v>
+        <v>56826906</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90932</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>646949.057189983</v>
+        <v>646949</v>
       </c>
       <c r="R3" t="n">
-        <v>7132738.141426084</v>
+        <v>7132744</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,21 +850,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,7 +871,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>mossig gammal tallåga</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -919,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>56826909</v>
+        <v>56826904</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>646964.9847554376</v>
+        <v>646920</v>
       </c>
       <c r="R4" t="n">
-        <v>7132760.212802144</v>
+        <v>7132912</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -992,21 +957,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,7 +978,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Gammeltall med brandljud</t>
+          <t>mossig gammal tallåga</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>56826914</v>
+        <v>56826905</v>
       </c>
       <c r="B5" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1081,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>647034.8137207236</v>
+        <v>646902</v>
       </c>
       <c r="R5" t="n">
-        <v>7132866.185823696</v>
+        <v>7132848</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1114,21 +1064,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,7 +1085,7 @@
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>törvedshögstubbe</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1163,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>56826912</v>
+        <v>56826909</v>
       </c>
       <c r="B6" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1203,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>647034.8137207236</v>
+        <v>646965</v>
       </c>
       <c r="R6" t="n">
-        <v>7132866.185823696</v>
+        <v>7132760</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1236,21 +1171,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1267,7 +1192,7 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>törvedshögstubbe</t>
+          <t>Gammeltall med brandljud</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1285,37 +1210,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>56826907</v>
+        <v>56826915</v>
       </c>
       <c r="B7" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1325,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>646949.057189983</v>
+        <v>646995</v>
       </c>
       <c r="R7" t="n">
-        <v>7132738.141426084</v>
+        <v>7132879</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1358,21 +1278,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1389,7 +1299,7 @@
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>björk</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1407,37 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>56826911</v>
+        <v>56826916</v>
       </c>
       <c r="B8" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1447,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>646975.1362646231</v>
+        <v>646957</v>
       </c>
       <c r="R8" t="n">
-        <v>7132812.015567784</v>
+        <v>7132944</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1480,21 +1385,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1406,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>brandstubbe</t>
+          <t>gran, ymnigt</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1529,15 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>56826905</v>
+        <v>56826912</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1545,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1569,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>646901.9998863166</v>
+        <v>647035</v>
       </c>
       <c r="R9" t="n">
-        <v>7132848.094738643</v>
+        <v>7132866</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,21 +1492,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1633,7 +1513,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>törvedshögstubbe</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1651,15 +1531,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>56826906</v>
+        <v>56826908</v>
       </c>
       <c r="B10" t="n">
-        <v>88476</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1667,21 +1542,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1691,10 +1566,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>646949.222035517</v>
+        <v>646949</v>
       </c>
       <c r="R10" t="n">
-        <v>7132743.803003789</v>
+        <v>7132738</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1724,21 +1599,11 @@
           <t>2015-05-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-10-30</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1755,7 +1620,7 @@
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>mossig gammal tallåga</t>
+          <t>brandstubbe</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1770,6 +1635,327 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>56826914</v>
+      </c>
+      <c r="B11" t="n">
+        <v>78334</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sör-Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>647035</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7132866</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>törvedshögstubbe</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>56826907</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sör-Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>646949</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7132738</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>56826911</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sör-Åliden, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>646975</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7132812</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Fredrika</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2015-05-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2015-10-30</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>barrnaturskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30076-2025 artfynd.xlsx
+++ b/artfynd/A 30076-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826903</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826906</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826904</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826905</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826909</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826915</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1421,6 +1456,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826916</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1528,6 +1568,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826912</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1635,6 +1680,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826908</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1742,6 +1792,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826914</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1849,6 +1904,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826907</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1956,8 +2016,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56826911</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>